--- a/crates/xlstream-eval/tests/fixtures/lookup/choose.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/lookup/choose.xlsx
@@ -20,9 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t xml:space="preserve">choose</t>
+    <t xml:space="preserve">idx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choose_text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choose_num</t>
   </si>
 </sst>
 </file>
@@ -295,18 +301,96 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="str">
-        <f aca="false">CHOOSE(2,"alpha","beta","gamma")</f>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="str">
+        <f aca="false">CHOOSE(A2,"alpha","beta","gamma")</f>
+        <v>alpha</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <f aca="false">CHOOSE(A2,100,200,300)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="str">
+        <f aca="false">CHOOSE(A3,"alpha","beta","gamma")</f>
         <v>beta</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <f aca="false">CHOOSE(A3,100,200,300)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="str">
+        <f aca="false">CHOOSE(A4,"alpha","beta","gamma")</f>
+        <v>gamma</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <f aca="false">CHOOSE(A4,100,200,300)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="0" t="str">
+        <f aca="false">CHOOSE(A5,"alpha","beta","gamma")</f>
+        <v>alpha</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <f aca="false">CHOOSE(A5,100,200,300)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="0" t="str">
+        <f aca="false">CHOOSE(A6,"alpha","beta","gamma")</f>
+        <v>beta</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <f aca="false">CHOOSE(A6,100,200,300)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="0" t="str">
+        <f aca="false">CHOOSE(A7,"alpha","beta","gamma")</f>
+        <v>gamma</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <f aca="false">CHOOSE(A7,100,200,300)</f>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
